--- a/output_excel/5232513.xlsx
+++ b/output_excel/5232513.xlsx
@@ -575,7 +575,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>P1-11 | 112,5KVA 1RU6A | RCAL70 112,5KVA 1RU6A | A3x1/0; A3x1/0(AQ1/0) 112,5KVA | 1RU6A 112,5KVA | C12/600;M3(3)F;,ET4A,S43(4);IP;TEL(CID:13) 8RL 2 V1-3 TX10 | xBM P2-4 | 1RU6A 112,5KVA</t>
+          <t>P1-11 | 112,5KVA 1RU6A | RCAL70 112,5KVA 1RU6A | A3x1/0; A3x1/0(AQ1/0) 112,5KVA | 1RU6A 112,5KVA | C12/600;M3(3)F; ET4A S43(4);IP;TEL(CID:13) 8RL 2 V1-3 TX10 | xBM P2-4 | 1RU6A 112,5KVA</t>
         </is>
       </c>
       <c r="L2" s="3" t="n">
